--- a/results/Int Task Remove ACC -0.3/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC -0.3/Rando_3_permute.xlsx
@@ -440,57 +440,57 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6561530529031813</v>
+        <v>0.6893669395028542</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6515377059035883</v>
+        <v>0.6808977993323639</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6718911129041305</v>
+        <v>0.6816877586154821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6721755270110703</v>
+        <v>0.6864598749584705</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6720176789795322</v>
+        <v>0.6879459476562984</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.688041591338278</v>
+        <v>0.6870930648981934</v>
       </c>
     </row>
     <row r="8">
@@ -500,827 +500,827 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6877255357124878</v>
+        <v>0.6870930648981934</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6599496756025192</v>
+        <v>0.7016934684713838</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6781528975720887</v>
+        <v>0.6954363581187104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6732229331975624</v>
+        <v>0.6761573245082261</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6776146321889172</v>
+        <v>0.6761573245082261</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6871912255191726</v>
+        <v>0.6761573245082261</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6831781460658806</v>
+        <v>0.6844369751283279</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6831781460658806</v>
+        <v>0.6775157524425095</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6783420275597629</v>
+        <v>0.6673048904843886</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6791323464055954</v>
+        <v>0.6652823502169601</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6699390469286872</v>
+        <v>0.6637653551257103</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6335308051759772</v>
+        <v>0.6617111733394315</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6549244271087274</v>
+        <v>0.6757449060750278</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6886434993218646</v>
+        <v>0.6667695016029306</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6947114796868641</v>
+        <v>0.6668011431217811</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7174685634318967</v>
+        <v>0.6668011431217811</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7190804830796977</v>
+        <v>0.6670833998524355</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7250855399697105</v>
+        <v>0.6673994554782257</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6793218359559838</v>
+        <v>0.6472060538855067</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6793218359559838</v>
+        <v>0.6205685693287253</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6085674446165551</v>
+        <v>0.631628718417809</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5953574700592128</v>
+        <v>0.6320713401190008</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5961790708611814</v>
+        <v>0.6657965248982798</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5944405851379786</v>
+        <v>0.6318239609716247</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5987704393424893</v>
+        <v>0.6427266215918848</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6004150791972834</v>
+        <v>0.641935583620624</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6017102240938661</v>
+        <v>0.6575172338408921</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.608409237022303</v>
+        <v>0.671267271594977</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6116337954433336</v>
+        <v>0.6993944244767284</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6082201070346287</v>
+        <v>0.6810944801370366</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6082517485534792</v>
+        <v>0.6797651767826041</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6170024263291956</v>
+        <v>0.7150706396908335</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6170024263291956</v>
+        <v>0.698698670624733</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.623166769501603</v>
+        <v>0.7034085826181631</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.63476446484843</v>
+        <v>0.7077700783415242</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.6122910760849085</v>
+        <v>0.7077700783415242</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6143114589760517</v>
+        <v>0.6945611824723245</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.600057314296645</v>
+        <v>0.6747780419365185</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5868423058613037</v>
+        <v>0.6698797190808427</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5920883258616201</v>
+        <v>0.667887741644122</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6010939336017109</v>
+        <v>0.6657688385692856</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.598629131195805</v>
+        <v>0.5846227252264886</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5993245254850861</v>
+        <v>0.5753629066474517</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5882036102973008</v>
+        <v>0.5602555196472259</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5686049254338843</v>
+        <v>0.526312439863136</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5775810490314099</v>
+        <v>0.5057084176507899</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5775810490314099</v>
+        <v>0.5163291811031097</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5571625611795958</v>
+        <v>0.569169079332479</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5731303817549249</v>
+        <v>0.5664213010704902</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5736682875753824</v>
+        <v>0.5632301819818809</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5836235004437004</v>
+        <v>0.5682230698313938</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5820777403353139</v>
+        <v>0.5672126986044652</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.6086285702779708</v>
+        <v>0.5612396427960172</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.620818824977815</v>
+        <v>0.5516004855534893</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6268569616375349</v>
+        <v>0.5626940739749946</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6474379718361717</v>
+        <v>0.5601972704875239</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6391921201112055</v>
+        <v>0.561429851471834</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5938785886156692</v>
+        <v>0.561429851471834</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5861986886028687</v>
+        <v>0.5631363361134722</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.585598218870139</v>
+        <v>0.5553938721883994</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5848726213128641</v>
+        <v>0.5425625171691196</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5765300472177757</v>
+        <v>0.5378867636335395</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.569261846512745</v>
+        <v>0.5256551592215611</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5631589885644674</v>
+        <v>0.5372848556499528</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5631273470456171</v>
+        <v>0.5381690203641939</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5931501145566808</v>
+        <v>0.5465763157478402</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5872353079079347</v>
+        <v>0.5349487766957337</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5998124520882684</v>
+        <v>0.5320420717140643</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6154545088445236</v>
+        <v>0.5320420717140643</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6079306590496901</v>
+        <v>0.505372226513004</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.556682185393412</v>
+        <v>0.5019908987485779</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5546574877496984</v>
+        <v>0.5018643326731762</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5589240589165081</v>
+        <v>0.4975974019436522</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.514943066839832</v>
+        <v>0.4996523028553594</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5157330261229502</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.552447974870881</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5332653040678049</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4999971234982863</v>
+        <v>0.5002844141069397</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5002186141302394</v>
+        <v>0.5002844141069397</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5006295943125808</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5010089329760719</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4981658705948174</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5002516938999466</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
